--- a/results/Int All Data -0.3/Rando_8_permute.xlsx
+++ b/results/Int All Data -0.3/Rando_8_permute.xlsx
@@ -440,1237 +440,1237 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7870210223139391</v>
+        <v>0.7719576287542498</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7884536870703862</v>
+        <v>0.7794791187255965</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7750595706459611</v>
+        <v>0.7736992814406818</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7786904107962053</v>
+        <v>0.7757796145909112</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7789799130008759</v>
+        <v>0.7761377807800229</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7805304200008907</v>
+        <v>0.8014460263966625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7769144261175527</v>
+        <v>0.7992478510028653</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7729940837626379</v>
+        <v>0.7992478510028653</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7733522499517497</v>
+        <v>0.7932128435055006</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7710854105735113</v>
+        <v>0.7956374244696172</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7771204180708761</v>
+        <v>0.7975804296509643</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7680679068248288</v>
+        <v>0.7918748237005805</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7704182564544145</v>
+        <v>0.7922673218819127</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7697019240761911</v>
+        <v>0.8002304882937186</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7739117686357766</v>
+        <v>0.8006573184672714</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.763662277120418</v>
+        <v>0.8010154846563832</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7613954377421797</v>
+        <v>0.7997201478688184</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7607477693483973</v>
+        <v>0.7984248110812536</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7563857505530234</v>
+        <v>0.7961579717030153</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.758559800763098</v>
+        <v>0.8007798001692474</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7611848063304483</v>
+        <v>0.7987829772703654</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7618324747242307</v>
+        <v>0.7919434876850215</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7697613091438158</v>
+        <v>0.7876798254079012</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7695061389313658</v>
+        <v>0.7894855026203661</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7712969698769245</v>
+        <v>0.7897406728328162</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7734802990038154</v>
+        <v>0.7897406728328162</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7706196089493297</v>
+        <v>0.7940043351099366</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7673812669804178</v>
+        <v>0.7897063408405957</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7726656101073386</v>
+        <v>0.7931850067550514</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7720179417135562</v>
+        <v>0.7836323618926021</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.763593613135977</v>
+        <v>0.7775092046854818</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7634711314340009</v>
+        <v>0.7683147260121442</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7638292976231127</v>
+        <v>0.7683147260121442</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7498803019730689</v>
+        <v>0.7599739076859124</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7477851225559333</v>
+        <v>0.7582174087325741</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.725494380687976</v>
+        <v>0.7582174087325741</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7440846905295664</v>
+        <v>0.7602290778983625</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7398599997030747</v>
+        <v>0.7602290778983625</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.74592933919266</v>
+        <v>0.74773223273008</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.74592933919266</v>
+        <v>0.749793080154995</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7600165907032677</v>
+        <v>0.7380079279065279</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7543054174027941</v>
+        <v>0.7332487714714135</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.746268947548139</v>
+        <v>0.7391316047329899</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.747019611918583</v>
+        <v>0.7404120952536484</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7393403803613581</v>
+        <v>0.7402107427587333</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7416072197395964</v>
+        <v>0.7287883961577861</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7419310539364876</v>
+        <v>0.7274243953857802</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7595108897367757</v>
+        <v>0.7207222337693187</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7411609038407292</v>
+        <v>0.684808186231572</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7479317294416319</v>
+        <v>0.6861230087444512</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7472497290556289</v>
+        <v>0.6226589292872307</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7421518921567172</v>
+        <v>0.6216874266965571</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7318727081075463</v>
+        <v>0.6213635924996659</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7238260314443933</v>
+        <v>0.6176102706474457</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7228545288537197</v>
+        <v>0.6165014400878899</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7295427720949568</v>
+        <v>0.5600290244518016</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7276489451727364</v>
+        <v>0.5678400166278189</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7258924462193981</v>
+        <v>0.5536163650400107</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7258581142271776</v>
+        <v>0.5506870110010837</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7214079457220481</v>
+        <v>0.5515063393559689</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7159667889009309</v>
+        <v>0.5535180085217571</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7169039594993839</v>
+        <v>0.5495976661668424</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7099614739373785</v>
+        <v>0.5581008655373606</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7099614739373785</v>
+        <v>0.5603333729233784</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7102853081342697</v>
+        <v>0.5716230310138516</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7020326395177933</v>
+        <v>0.5612362115296109</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6669026604510296</v>
+        <v>0.5562116780735484</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6679428270261443</v>
+        <v>0.5564714877444067</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6679428270261443</v>
+        <v>0.5545674540136882</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6605781507489942</v>
+        <v>0.5638946211974999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6654013317101415</v>
+        <v>0.563830596671467</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6897621999198301</v>
+        <v>0.5507798001692474</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6519682438350877</v>
+        <v>0.5548968555606693</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6523755882833262</v>
+        <v>0.5469485354157697</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6530919206615496</v>
+        <v>0.5520315260477753</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.644019923690188</v>
+        <v>0.548464710423564</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6204987974523806</v>
+        <v>0.5179519203646243</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6023789286933801</v>
+        <v>0.5252330863904271</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5831019790073786</v>
+        <v>0.5238690856184213</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5854718143622786</v>
+        <v>0.5235109194293095</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5860851507638405</v>
+        <v>0.5260180827530917</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6062797853229805</v>
+        <v>0.5258315765250827</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6073542838903158</v>
+        <v>0.5258315765250827</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.591908598957792</v>
+        <v>0.5144732544501686</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5925562673515744</v>
+        <v>0.5184130825303978</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5923697611235655</v>
+        <v>0.5197427513101831</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.607172417120715</v>
+        <v>0.5197427513101831</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5993957569369182</v>
+        <v>0.5209007601288657</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5961722612349125</v>
+        <v>0.5228437653102128</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5965647594162448</v>
+        <v>0.5228437653102128</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5776608221862612</v>
+        <v>0.521548428522648</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5759729872173642</v>
+        <v>0.522981093279095</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5759729872173642</v>
+        <v>0.523167599507104</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5638148225128792</v>
+        <v>0.5172457947948988</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5638148225128792</v>
+        <v>0.5179964591653429</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5688439954273498</v>
+        <v>0.5172801267871193</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5303142212390695</v>
+        <v>0.5176726249684517</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5168022625710764</v>
+        <v>0.5201797882922339</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5416382113217632</v>
+        <v>0.5194977879062309</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5412800451326514</v>
+        <v>0.5201797882922339</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5412800451326514</v>
+        <v>0.5184232893388957</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5431005686120225</v>
+        <v>0.5184232893388957</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5431005686120225</v>
+        <v>0.5172309485279926</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5577658966402897</v>
+        <v>0.5179816128984367</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5577658966402897</v>
+        <v>0.5188501195124485</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5490028875989132</v>
+        <v>0.5181337871342251</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.4981841159790371</v>
+        <v>0.5122658001395549</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5017657778701545</v>
+        <v>0.5080067773208427</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5001076354350699</v>
+        <v>0.5087231096990662</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.4955201389610583</v>
+        <v>0.5147089389373042</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.4965946375283935</v>
+        <v>0.5143507727481925</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5006328221268762</v>
+        <v>0.5136001083777484</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4993866635984382</v>
+        <v>0.5129867719761866</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.4997448297875499</v>
+        <v>0.5129867719761866</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.501177494543997</v>
+        <v>0.5129867719761866</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.501177494543997</v>
+        <v>0.5133449381652984</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5015013287408882</v>
+        <v>0.5112302730228484</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5005298261502146</v>
+        <v>0.5133106061730778</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4970854922279793</v>
+        <v>0.5161416036937512</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4970854922279793</v>
+        <v>0.5205722864735662</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4958931514170762</v>
+        <v>0.5205379544813457</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4952454830232938</v>
+        <v>0.5202827842688955</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4967959900233087</v>
+        <v>0.5190561114657719</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4957901554404145</v>
+        <v>0.5206261041911012</v>
       </c>
     </row>
     <row r="126">
@@ -1680,137 +1680,137 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4896373056994819</v>
+        <v>0.523167599507104</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4957901554404145</v>
+        <v>0.5108721068337366</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.498380829015544</v>
+        <v>0.5108721068337366</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4990284974093264</v>
+        <v>0.5108721068337366</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4990284974093264</v>
+        <v>0.5035417625488071</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4993866635984382</v>
+        <v>0.499111079768992</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4964721558264175</v>
+        <v>0.499111079768992</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.498380829015544</v>
+        <v>0.4982574194218863</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.498380829015544</v>
+        <v>0.4908240791602952</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.498380829015544</v>
+        <v>0.4907210831836335</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4987389952046558</v>
+        <v>0.4907210831836335</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4993523316062176</v>
+        <v>0.4972024065798655</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4993523316062176</v>
+        <v>0.4993857357067565</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4993523316062176</v>
+        <v>0.4927763632584586</v>
       </c>
     </row>
     <row r="140">
@@ -1820,167 +1820,167 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5003581661891118</v>
+        <v>0.4927865700669567</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4977331606217616</v>
+        <v>0.4907210831836335</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4977331606217616</v>
+        <v>0.4891705761836186</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4977331606217616</v>
+        <v>0.4917612497587482</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4988076591890969</v>
+        <v>0.4776591519812343</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4993523316062176</v>
+        <v>0.4892689327018721</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5000343319922206</v>
+        <v>0.4946024540879196</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5000343319922206</v>
+        <v>0.4946024540879196</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5000343319922206</v>
+        <v>0.4951127945128198</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5</v>
+        <v>0.4928459551345814</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5</v>
+        <v>0.4918744525439078</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5</v>
+        <v>0.4934249595439227</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5</v>
+        <v>0.4934249595439227</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5</v>
+        <v>0.4934249595439227</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5</v>
+        <v>0.498370622207046</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5</v>
+        <v>0.4987928129221907</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5</v>
+        <v>0.4992688213548703</v>
       </c>
     </row>
   </sheetData>
